--- a/stories/arbres/ATOM-JEU.REG.002-03.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Iris est au parc avec papa. Une marelle est dessinée. Papa dit une règle. La règle : on attend. Puis on saute une case. Iris veut sauter tout de suite. Papa va rappeler la règle une fois. Il dit : on attend. C'est la règle. Iris attend. Puis elle saute une case. Papa dit : tu as suivi la règle. Iris répète : une règle. Papa la rappelle. Iris la suit.</t>
+          <t>Iris est au parc avec papa. Une marelle est dessinée. Papa dit une règle. La règle : on attend. Puis on saute une case. Iris veut sauter tout de suite. Papa va rappeler la règle une fois. On attend. C'est la règle. Iris attend. Puis elle saute une case. Tu as suivi la règle. Iris répète : une règle. Papa la rappelle. Iris la suit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Iris est au parc avec papa. Une marelle est dessinée. Papa dit une règle. La règle : on attend. Puis on saute une case. Iris veut sauter tout de suite. Papa va rappeler la règle une fois.
+narrateur|On attend. C'est la règle.
+narrateur|Iris attend. Puis elle saute une case.
+papa|Tu as suivi la règle.
+narrateur|Iris répète : une règle. Papa la rappelle. Iris la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Iris joue. Que suit-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Iris a suivi la règle. Papa l'a rappelée. Iris a attendu, puis elle a sauté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range la craie. Iris donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-03.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Iris répète : une règle. Papa la rappelle. Iris la suit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Iris joue. Que suit-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Iris a suivi la règle. Papa l'a rappelée. Iris a attendu, puis elle a sauté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1847,7 @@
           <t>narrateur|Papa range la craie. Iris donne la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.REG.002-03.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Iris suit la règle de la marelle</t>
+          <t>La marelle de Victorina au parc</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>À l'ombre du platane, Victorina attend, puis saute une case. Papa rappelle la règle une fois.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Iris est au parc avec papa. Une marelle est dessinée. Papa dit une règle. La règle : on attend. Puis on saute une case. Iris veut sauter tout de suite. Papa va rappeler la règle une fois. On attend. C'est la règle. Iris attend. Puis elle saute une case. Tu as suivi la règle. Iris répète : une règle. Papa la rappelle. Iris la suit.</t>
+          <t>L'ombre du platane est fraîche sur le sol. Un peu de craie blanche poudre les cases. Un pigeon marche près de la case un. Ses pattes font des petits bruits. Le parc sent l'herbe coupée. Une marelle grise et blanche attend. Un bout de craie repose près du banc. Le vent agite une feuille du platane. Un banc de bois a des traces de craie. Une gourde bleue repose dessus. Loin, une cloche d'école sonne un peu. Tu as vu le pigeon, Victorina ? Oui, papa. Il marche tout doux. En ce moment, papa montre la première case. La craie colle un peu aux doigts. Une règle. On attend. Puis on saute une case. J'ai envie de sauter. On attend. Je te la rappelle une fois. C'est la règle. Victorina attend, les pieds près du trait. Puis elle saute une case. La craie fait un petit nuage blanc. C'est blanc, papa. Tu as suivi la règle. Tu as attendu. Bravo, Victorina. On attend. Puis on saute une case. Oui. Une règle simple. Je la rappelle une fois. Victorina attend encore. Puis elle saute la case suivante. Tu as suivi la règle dite. Bravo. Tu as fait du bon travail. Une règle. On attend. Oui. On la rappelle. Tu la suis. Le pigeon s'envole vers le banc. L'ombre du platane a un peu bougé. Encore une case, tout doux ? Oui, papa. Victorina attend. Puis elle saute une case. Bravo. Tu as attendu. Le bout de craie reste près du banc. J'ai suivi la règle. Oui. Une règle. On la rappelle. Victorina souffle. La craie poudre ses chaussures. On range la craie après, d'accord ? D'accord. J'ai attendu. Le platane fait un bruit de feuilles. Tu as les pieds près du trait ? Oui. J'ai attendu. Bravo. Une règle. On la rappelle. Victorina souffle encore. Un peu de craie reste sur son genou.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,61 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Iris est au parc avec papa. Une marelle est dessinée. Papa dit une règle. La règle : on attend. Puis on saute une case. Iris veut sauter tout de suite. Papa va rappeler la règle une fois.
-narrateur|On attend. C'est la règle.
-narrateur|Iris attend. Puis elle saute une case.
+          <t>narrateur|L'ombre du platane est fraîche sur le sol.
+narrateur|Un peu de craie blanche poudre les cases.
+narrateur|Un pigeon marche près de la case un.
+narrateur|Ses pattes font des petits bruits.
+narrateur|Le parc sent l'herbe coupée.
+narrateur|Une marelle grise et blanche attend.
+narrateur|Un bout de craie repose près du banc.
+narrateur|Le vent agite une feuille du platane.
+narrateur|Un banc de bois a des traces de craie.
+narrateur|Une gourde bleue repose dessus.
+narrateur|Loin, une cloche d'école sonne un peu.
+papa|Tu as vu le pigeon, Victorina ?
+enfant-f|Oui, papa. Il marche tout doux.
+narrateur|En ce moment, papa montre la première case.
+narrateur|La craie colle un peu aux doigts.
+papa|Une règle. On attend.
+papa|Puis on saute une case.
+enfant-f|J'ai envie de sauter.
+papa|On attend. Je te la rappelle une fois.
+papa|C'est la règle.
+narrateur|Victorina attend, les pieds près du trait.
+narrateur|Puis elle saute une case.
+narrateur|La craie fait un petit nuage blanc.
+enfant-f|C'est blanc, papa.
 papa|Tu as suivi la règle.
-narrateur|Iris répète : une règle. Papa la rappelle. Iris la suit.</t>
+papa|Tu as attendu. Bravo, Victorina.
+enfant-f|On attend. Puis on saute une case.
+papa|Oui. Une règle simple.
+papa|Je la rappelle une fois.
+narrateur|Victorina attend encore.
+narrateur|Puis elle saute la case suivante.
+papa|Tu as suivi la règle dite.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Une règle. On attend.
+papa|Oui. On la rappelle. Tu la suis.
+narrateur|Le pigeon s'envole vers le banc.
+narrateur|L'ombre du platane a un peu bougé.
+papa|Encore une case, tout doux ?
+enfant-f|Oui, papa.
+narrateur|Victorina attend.
+narrateur|Puis elle saute une case.
+papa|Bravo. Tu as attendu.
+narrateur|Le bout de craie reste près du banc.
+enfant-f|J'ai suivi la règle.
+papa|Oui. Une règle. On la rappelle.
+narrateur|Victorina souffle.
+narrateur|La craie poudre ses chaussures.
+papa|On range la craie après, d'accord ?
+enfant-f|D'accord. J'ai attendu.
+narrateur|Le platane fait un bruit de feuilles.
+papa|Tu as les pieds près du trait ?
+enfant-f|Oui. J'ai attendu.
+papa|Bravo. Une règle. On la rappelle.
+narrateur|Victorina souffle encore.
+narrateur|Un peu de craie reste sur son genou.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,7 +1410,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Iris joue. Que suit-elle ?</t>
+          <t>Victorina joue. Que suit-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,10 +1566,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Iris joue. Que suit-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Victorina joue.
+narrateur|Que suit-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Iris a suivi la règle. Papa l'a rappelée. Iris a attendu, puis elle a sauté.</t>
+          <t>Victorina a suivi la règle. Papa l'a rappelée une fois. Elle a attendu, puis elle a sauté. Tu as suivi la règle, Victorina ? Oui. Une règle. On attend. Bravo. On la rappelle, et on la suit. La craie blanche reste sur les cases.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,10 +1738,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Iris a suivi la règle. Papa l'a rappelée. Iris a attendu, puis elle a sauté.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorina a suivi la règle.
+narrateur|Papa l'a rappelée une fois.
+narrateur|Elle a attendu, puis elle a sauté.
+papa|Tu as suivi la règle, Victorina ?
+enfant-f|Oui. Une règle. On attend.
+papa|Bravo. On la rappelle, et on la suit.
+narrateur|La craie blanche reste sur les cases.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,7 +1771,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range la craie. Iris donne la main.</t>
+          <t>On range la craie ? Oui, papa. Papa range la craie dans sa poche. Victorina donne la main. On rentre tout doux ? Oui. Le pigeon est parti. L'ombre du platane reste fraîche. La gourde est encore sur le banc. On la prend ? Oui. Puis on rentre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,10 +1911,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range la craie. Iris donne la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>papa|On range la craie ?
+enfant-f|Oui, papa.
+narrateur|Papa range la craie dans sa poche.
+narrateur|Victorina donne la main.
+papa|On rentre tout doux ?
+enfant-f|Oui. Le pigeon est parti.
+narrateur|L'ombre du platane reste fraîche.
+papa|La gourde est encore sur le banc.
+enfant-f|On la prend ?
+papa|Oui. Puis on rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,7 +1947,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La main de Victorina est un peu blanche. J'ai attendu. Puis j'ai sauté. Oui. Tu as suivi la règle. Bravo, Victorina. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,10 +2087,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La main de Victorina est un peu blanche.
+enfant-f|J'ai attendu. Puis j'ai sauté.
+papa|Oui. Tu as suivi la règle.
+papa|Bravo, Victorina.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2150,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-03.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'ombre du platane est fraîche sur le sol. Un peu de craie blanche poudre les cases. Un pigeon marche près de la case un. Ses pattes font des petits bruits. Le parc sent l'herbe coupée. Une marelle grise et blanche attend. Un bout de craie repose près du banc. Le vent agite une feuille du platane. Un banc de bois a des traces de craie. Une gourde bleue repose dessus. Loin, une cloche d'école sonne un peu. Tu as vu le pigeon, Victorina ? Oui, papa. Il marche tout doux. En ce moment, papa montre la première case. La craie colle un peu aux doigts. Une règle. On attend. Puis on saute une case. J'ai envie de sauter. On attend. Je te la rappelle une fois. C'est la règle. Victorina attend, les pieds près du trait. Puis elle saute une case. La craie fait un petit nuage blanc. C'est blanc, papa. Tu as suivi la règle. Tu as attendu. Bravo, Victorina. On attend. Puis on saute une case. Oui. Une règle simple. Je la rappelle une fois. Victorina attend encore. Puis elle saute la case suivante. Tu as suivi la règle dite. Bravo. Tu as fait du bon travail. Une règle. On attend. Oui. On la rappelle. Tu la suis. Le pigeon s'envole vers le banc. L'ombre du platane a un peu bougé. Encore une case, tout doux ? Oui, papa. Victorina attend. Puis elle saute une case. Bravo. Tu as attendu. Le bout de craie reste près du banc. J'ai suivi la règle. Oui. Une règle. On la rappelle. Victorina souffle. La craie poudre ses chaussures. On range la craie après, d'accord ? D'accord. J'ai attendu. Le platane fait un bruit de feuilles. Tu as les pieds près du trait ? Oui. J'ai attendu. Bravo. Une règle. On la rappelle. Victorina souffle encore. Un peu de craie reste sur son genou.</t>
+          <t>L'ombre du platane est fraîche sur le sol. Un peu de craie blanche poudre les cases. Un pigeon marche près de la case un. Ses pattes font des petits bruits. Le parc sent l'herbe coupée. Une marelle grise et blanche attend. Un bout de craie repose près du banc. Le vent agite une feuille du platane. Un banc de bois a des traces de craie. Une gourde bleue repose dessus. Loin, une cloche d'école sonne un peu. Tu as vu le pigeon, Victorina ? Oui, papa. Il marche tout doux. En ce moment, papa montre la première case. La craie colle un peu aux doigts. Une règle. On attend. Puis on saute une case. J'ai envie de sauter. On attend. Je te la rappelle une fois. C'est la règle. Victorina attend, les pieds près du trait. Puis elle saute une case. La craie fait un petit nuage blanc. C'est blanc, papa. Tu as suivi la règle. Tu as attendu. Bravo, Victorina. On attend. Puis on saute une case. Oui. Une règle simple. Je la rappelle une fois. Victorina attend encore. Puis elle saute la case suivante. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. Le pigeon s'envole vers le banc. L'ombre du platane a un peu bougé. Encore une case, tout doux ? Oui, papa. Victorina attend. Puis elle saute une case. Bravo. Tu as attendu. Le bout de craie reste près du banc. J'ai suivi la règle. Oui. Une règle. On la rappelle. Victorina souffle. La craie poudre ses chaussures. On range la craie après, d'accord ? D'accord. J'ai attendu. Le platane fait un bruit de feuilles. Tu as les pieds près du trait ? Oui. J'ai attendu. Bravo. Une règle. On la rappelle. Victorina souffle encore. Un peu de craie reste sur son genou.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Iris est au parc avec papa. &lt;emphasis level="moderate"&gt;une&lt;/emphasis&gt; marelle est dessinée. Papa dit une règle. La règle : on attend. Puis on saute une case. Iris veut sauter tout de suite. Papa va rappeler la règle une fois. Il dit : on attend. C'est la règle. Iris attend. Puis elle saute une case. Papa dit : tu as suivi la règle. Iris répète : une règle. Papa la rappelle. Iris la suit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'ombre du platane est fraîche sur le sol. Un peu de craie blanche poudre les cases. Un pigeon marche près de la case un. Ses pattes font des petits bruits. Le parc sent l'herbe coupée. Une marelle grise et blanche attend. Un bout de craie repose près du banc. Le vent agite une feuille du platane. Un banc de bois a des traces de craie. Une gourde bleue repose dessus. Loin, une cloche d'école sonne un peu. Tu as vu le pigeon, Victorina ? Oui, papa. Il marche tout doux. En ce moment, papa montre la première case. La craie colle un peu aux doigts. Une règle. On attend. Puis on saute une case. J'ai envie de sauter. On attend. Je te la rappelle une fois. C'est la règle. Victorina attend, les pieds près du trait. Puis elle saute une case. La craie fait un petit nuage blanc. C'est blanc, papa. Tu as suivi la règle. Tu as attendu. Bravo, Victorina. On attend. Puis on saute une case. Oui. Une règle simple. Je la rappelle une fois. Victorina attend encore. Puis elle saute la case suivante. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. Le pigeon s'envole vers le banc. L'ombre du platane a un peu bougé. Encore une case, tout doux ? Oui, papa. Victorina attend. Puis elle saute une case. Bravo. Tu as attendu. Le bout de craie reste près du banc. J'ai suivi la règle. Oui. Une règle. On la rappelle. Victorina souffle. La craie poudre ses chaussures. On range la craie après, d'accord ? D'accord. J'ai attendu. Le platane fait un bruit de feuilles. Tu as les pieds près du trait ? Oui. J'ai attendu. Bravo. Une règle. On la rappelle. Victorina souffle encore. Un peu de craie reste sur son genou.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1356,7 +1356,6 @@
 narrateur|Victorina attend encore.
 narrateur|Puis elle saute la case suivante.
 papa|Tu as suivi la règle dite.
-papa|Bravo. Tu as fait du bon travail.
 enfant-f|Une règle. On attend.
 papa|Oui. On la rappelle. Tu la suis.
 narrateur|Le pigeon s'envole vers le banc.
@@ -1415,7 +1414,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Iris joue. Que suit-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina joue. Que suit-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1599,7 +1598,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Iris a suivi &lt;emphasis level="moderate"&gt;la&lt;/emphasis&gt; règle. Papa l'a rappelée. Iris a attendu, puis elle a sauté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a suivi la règle. Papa l'a rappelée une fois. Elle a attendu, puis elle a sauté. Tu as suivi la règle, Victorina ? Oui. Une règle. On attend. Bravo. On la rappelle, et on la suit. La craie blanche reste sur les cases.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1776,7 +1775,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range &lt;emphasis level="moderate"&gt;la&lt;/emphasis&gt; craie. Iris donne la main.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range la craie ? Oui, papa. Papa range la craie dans sa poche. Victorina donne la main. On rentre tout doux ? Oui. Le pigeon est parti. L'ombre du platane reste fraîche. La gourde est encore sur le banc. On la prend ? Oui. Puis on rentre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1947,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La main de Victorina est un peu blanche. J'ai attendu. Puis j'ai sauté. Oui. Tu as suivi la règle. Bravo, Victorina. L'histoire est finie.</t>
+          <t>La main de Victorina est un peu blanche. J'ai attendu. Puis j'ai sauté. Oui. Tu as suivi la règle. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La main de Victorina est un peu blanche. J'ai attendu. Puis j'ai sauté. Oui. Tu as suivi la règle. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2090,8 +2089,7 @@
           <t>narrateur|La main de Victorina est un peu blanche.
 enfant-f|J'ai attendu. Puis j'ai sauté.
 papa|Oui. Tu as suivi la règle.
-papa|Bravo, Victorina.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Victorina.</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2157,6 +2155,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-03.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc</t>
+          <t>parc, platane, marelle à la craie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Iris, papa</t>
+          <t>Victorina, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-03.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-03.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La marelle de Victorina au parc</t>
+          <t>La marelle de la rivière</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc, platane, marelle à la craie</t>
+          <t>parc au bord de la rivière, automne, craie jaune</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Victorina, papa</t>
+          <t>Sarah, Chouchou, papa</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>À l'ombre du platane, Victorina attend, puis saute une case. Papa rappelle la règle une fois.</t>
+          <t>Sarah veut sauter jusqu'au bout de la marelle. Elle saute trop tôt, la craie s'efface, Chouchou perd son caillou. Elles attendent un peu. Une après l'autre, le bout reste jaune. La rivière brille.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'ombre du platane est fraîche sur le sol. Un peu de craie blanche poudre les cases. Un pigeon marche près de la case un. Ses pattes font des petits bruits. Le parc sent l'herbe coupée. Une marelle grise et blanche attend. Un bout de craie repose près du banc. Le vent agite une feuille du platane. Un banc de bois a des traces de craie. Une gourde bleue repose dessus. Loin, une cloche d'école sonne un peu. Tu as vu le pigeon, Victorina ? Oui, papa. Il marche tout doux. En ce moment, papa montre la première case. La craie colle un peu aux doigts. Une règle. On attend. Puis on saute une case. J'ai envie de sauter. On attend. Je te la rappelle une fois. C'est la règle. Victorina attend, les pieds près du trait. Puis elle saute une case. La craie fait un petit nuage blanc. C'est blanc, papa. Tu as suivi la règle. Tu as attendu. Bravo, Victorina. On attend. Puis on saute une case. Oui. Une règle simple. Je la rappelle une fois. Victorina attend encore. Puis elle saute la case suivante. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. Le pigeon s'envole vers le banc. L'ombre du platane a un peu bougé. Encore une case, tout doux ? Oui, papa. Victorina attend. Puis elle saute une case. Bravo. Tu as attendu. Le bout de craie reste près du banc. J'ai suivi la règle. Oui. Une règle. On la rappelle. Victorina souffle. La craie poudre ses chaussures. On range la craie après, d'accord ? D'accord. J'ai attendu. Le platane fait un bruit de feuilles. Tu as les pieds près du trait ? Oui. J'ai attendu. Bravo. Une règle. On la rappelle. Victorina souffle encore. Un peu de craie reste sur son genou.</t>
+          <t>La craie jaune sent encore le papier. Le parc descend vers la rivière. Les châtaignes tapent l'herbe, toutes brunes. Un bateau passe, très loin, tout bas. Le banc de bois est froid d'un côté. L'autre côté a pris le soleil. Sarah, tu vois les cases ? Oui, papa. Elles sont jaunes. Chouchou tient un caillou plat. Le caillou est gris, un peu mouillé. Je commence. C'est mon caillou. En ce moment, Sarah se penche déjà. Je saute. Jusqu'au bout. Chouchou n'a pas encore posé. Sarah saute quand même. Son pied écrase une case. La craie devient une poudre grise. Le caillou de Chouchou glisse. Il part dans l'herbe. Oh. Mon caillou. Chouchou a les joues toutes plates. Elle ne saute plus. La marelle s'est arrêtée. On attend un peu ? Je voulais le bout. Le bout est encore là. Chouchou d'abord. Sarah s'arrête au bord des cases. Ses chaussures ont de la craie. Ça sent la poussière chaude. Je ramasse le caillou ? Oui. Tout doux, dans l'herbe. Sarah cherche près d'une châtaigne. Le caillou est froid, un peu mouillé. Le voilà. Merci. Chouchou le pose sur la première case. La craie tient, cette fois. Tu attends le tour de Chouchou ? Oui. On attend un peu. Sarah reste sur le banc tiède. Elle entend la rivière, tout bas. Chouchou saute une case, puis l'autre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>L'ombre du platane est fraîche sur le sol. Un peu de craie blanche poudre les cases. Un pigeon marche près de la case un. Ses pattes font des petits bruits. Le parc sent l'herbe coupée. Une marelle grise et blanche attend. Un bout de craie repose près du banc. Le vent agite une feuille du platane. Un banc de bois a des traces de craie. Une gourde bleue repose dessus. Loin, une cloche d'école sonne un peu. Tu as vu le pigeon, Victorina ? Oui, papa. Il marche tout doux. En ce moment, papa montre la première case. La craie colle un peu aux doigts. Une règle. On attend. Puis on saute une case. J'ai envie de sauter. On attend. Je te la rappelle une fois. C'est la règle. Victorina attend, les pieds près du trait. Puis elle saute une case. La craie fait un petit nuage blanc. C'est blanc, papa. Tu as suivi la règle. Tu as attendu. Bravo, Victorina. On attend. Puis on saute une case. Oui. Une règle simple. Je la rappelle une fois. Victorina attend encore. Puis elle saute la case suivante. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. Le pigeon s'envole vers le banc. L'ombre du platane a un peu bougé. Encore une case, tout doux ? Oui, papa. Victorina attend. Puis elle saute une case. Bravo. Tu as attendu. Le bout de craie reste près du banc. J'ai suivi la règle. Oui. Une règle. On la rappelle. Victorina souffle. La craie poudre ses chaussures. On range la craie après, d'accord ? D'accord. J'ai attendu. Le platane fait un bruit de feuilles. Tu as les pieds près du trait ? Oui. J'ai attendu. Bravo. Une règle. On la rappelle. Victorina souffle encore. Un peu de craie reste sur son genou.</t>
+          <t>La craie jaune sent encore le papier. Le parc descend vers la rivière. Les châtaignes tapent l'herbe, toutes brunes. Un bateau passe, très loin, tout bas. Le banc de bois est froid d'un côté. L'autre côté a pris le soleil. Sarah, tu vois les cases ? Oui, papa. Elles sont jaunes. Chouchou tient un caillou plat. Le caillou est gris, un peu mouillé. Je commence. C'est mon caillou. En ce moment, Sarah se penche déjà. Je saute. Jusqu'au bout. Chouchou n'a pas encore posé. Sarah saute quand même. Son pied écrase une case. La craie devient une poudre grise. Le caillou de Chouchou glisse. Il part dans l'herbe. Oh. Mon caillou. Chouchou a les joues toutes plates. Elle ne saute plus. La marelle s'est arrêtée. On attend un peu ? Je voulais le bout. Le bout est encore là. Chouchou d'abord. Sarah s'arrête au bord des cases. Ses chaussures ont de la craie. Ça sent la poussière chaude. Je ramasse le caillou ? Oui. Tout doux, dans l'herbe. Sarah cherche près d'une châtaigne. Le caillou est froid, un peu mouillé. Le voilà. Merci. Chouchou le pose sur la première case. La craie tient, cette fois. Tu attends le tour de Chouchou ? Oui. On attend un peu. Sarah reste sur le banc tiède. Elle entend la rivière, tout bas. Chouchou saute une case, puis l'autre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,60 +1324,55 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|L'ombre du platane est fraîche sur le sol.
-narrateur|Un peu de craie blanche poudre les cases.
-narrateur|Un pigeon marche près de la case un.
-narrateur|Ses pattes font des petits bruits.
-narrateur|Le parc sent l'herbe coupée.
-narrateur|Une marelle grise et blanche attend.
-narrateur|Un bout de craie repose près du banc.
-narrateur|Le vent agite une feuille du platane.
-narrateur|Un banc de bois a des traces de craie.
-narrateur|Une gourde bleue repose dessus.
-narrateur|Loin, une cloche d'école sonne un peu.
-papa|Tu as vu le pigeon, Victorina ?
-enfant-f|Oui, papa. Il marche tout doux.
-narrateur|En ce moment, papa montre la première case.
-narrateur|La craie colle un peu aux doigts.
-papa|Une règle. On attend.
-papa|Puis on saute une case.
-enfant-f|J'ai envie de sauter.
-papa|On attend. Je te la rappelle une fois.
-papa|C'est la règle.
-narrateur|Victorina attend, les pieds près du trait.
-narrateur|Puis elle saute une case.
-narrateur|La craie fait un petit nuage blanc.
-enfant-f|C'est blanc, papa.
-papa|Tu as suivi la règle.
-papa|Tu as attendu. Bravo, Victorina.
-enfant-f|On attend. Puis on saute une case.
-papa|Oui. Une règle simple.
-papa|Je la rappelle une fois.
-narrateur|Victorina attend encore.
-narrateur|Puis elle saute la case suivante.
-papa|Tu as suivi la règle dite.
-enfant-f|Une règle. On attend.
-papa|Oui. On la rappelle. Tu la suis.
-narrateur|Le pigeon s'envole vers le banc.
-narrateur|L'ombre du platane a un peu bougé.
-papa|Encore une case, tout doux ?
+          <t>narrateur|La craie jaune sent encore le papier.
+narrateur|Le parc descend vers la rivière.
+narrateur|Les châtaignes tapent l'herbe, toutes brunes.
+narrateur|Un bateau passe, très loin, tout bas.
+narrateur|Le banc de bois est froid d'un côté.
+narrateur|L'autre côté a pris le soleil.
+papa|Sarah, tu vois les cases ?
 enfant-f|Oui, papa.
-narrateur|Victorina attend.
-narrateur|Puis elle saute une case.
-papa|Bravo. Tu as attendu.
-narrateur|Le bout de craie reste près du banc.
-enfant-f|J'ai suivi la règle.
-papa|Oui. Une règle. On la rappelle.
-narrateur|Victorina souffle.
-narrateur|La craie poudre ses chaussures.
-papa|On range la craie après, d'accord ?
-enfant-f|D'accord. J'ai attendu.
-narrateur|Le platane fait un bruit de feuilles.
-papa|Tu as les pieds près du trait ?
-enfant-f|Oui. J'ai attendu.
-papa|Bravo. Une règle. On la rappelle.
-narrateur|Victorina souffle encore.
-narrateur|Un peu de craie reste sur son genou.</t>
+enfant-f|Elles sont jaunes.
+narrateur|Chouchou tient un caillou plat.
+narrateur|Le caillou est gris, un peu mouillé.
+copine|Je commence.
+copine|C'est mon caillou.
+narrateur|En ce moment, Sarah se penche déjà.
+enfant-f|Je saute.
+enfant-f|Jusqu'au bout.
+papa|Chouchou n'a pas encore posé.
+narrateur|Sarah saute quand même.
+narrateur|Son pied écrase une case.
+narrateur|La craie devient une poudre grise.
+narrateur|Le caillou de Chouchou glisse.
+narrateur|Il part dans l'herbe.
+copine|Oh.
+copine|Mon caillou.
+narrateur|Chouchou a les joues toutes plates.
+narrateur|Elle ne saute plus.
+papa|La marelle s'est arrêtée.
+papa|On attend un peu ?
+enfant-f|Je voulais le bout.
+papa|Le bout est encore là.
+papa|Chouchou d'abord.
+narrateur|Sarah s'arrête au bord des cases.
+narrateur|Ses chaussures ont de la craie.
+narrateur|Ça sent la poussière chaude.
+enfant-f|Je ramasse le caillou ?
+papa|Oui.
+papa|Tout doux, dans l'herbe.
+narrateur|Sarah cherche près d'une châtaigne.
+narrateur|Le caillou est froid, un peu mouillé.
+enfant-f|Le voilà.
+copine|Merci.
+narrateur|Chouchou le pose sur la première case.
+narrateur|La craie tient, cette fois.
+papa|Tu attends le tour de Chouchou ?
+enfant-f|Oui.
+papa|On attend un peu.
+narrateur|Sarah reste sur le banc tiède.
+narrateur|Elle entend la rivière, tout bas.
+narrateur|Chouchou saute une case, puis l'autre.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1409,12 +1404,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Victorina joue. Que suit-elle ?</t>
+          <t>Sarah veut sauter. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Victorina joue. Que suit-elle ?</t>
+          <t>Sarah veut sauter. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1424,12 +1419,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>la règle</t>
+          <t>attendre</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>la règle | une règle | attendre | la rappeler</t>
+          <t>attendre | on attend | un peu | son tour | elle attend | il attend | attendre un peu | on attend un peu | à son tour</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1444,7 +1439,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Papa rappelle. Quelle chose Iris suit ?</t>
+          <t>Elle reste un peu. Que fait Sarah d'abord ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1486,14 +1481,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1565,8 +1560,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Victorina joue.
-narrateur|Que suit-elle ?</t>
+          <t>narrateur|Sarah veut sauter.
+narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1588,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a suivi la règle. Papa l'a rappelée une fois. Elle a attendu, puis elle a sauté. Tu as suivi la règle, Victorina ? Oui. Une règle. On attend. Bravo. On la rappelle, et on la suit. La craie blanche reste sur les cases.</t>
+          <t>Chouchou arrive au bout des cases. C'est bon. À toi. Sarah, tu peux y aller. J'y vais. Elle pose le caillou sur une case. Elle saute, un pied, puis l'autre. La craie reste jaune, pas grise. Je n'ai pas écrasé. Oui. Les cases tiennent. Chouchou tape des mains, tout petit. Un bateau glisse encore, plus loin. Encore une fois ? Encore. On attend un peu. Sarah revient près du banc. Chouchou reprend le caillou gris. Moi d'abord. Toi d'abord. Chouchou saute. Sarah compte les cases, sans bouger. Merci, Sarah. Le bout est jaune.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a suivi la règle. Papa l'a rappelée une fois. Elle a attendu, puis elle a sauté. Tu as suivi la règle, Victorina ? Oui. Une règle. On attend. Bravo. On la rappelle, et on la suit. La craie blanche reste sur les cases.</t>
+          <t>Chouchou arrive au bout des cases. C'est bon. À toi. Sarah, tu peux y aller. J'y vais. Elle pose le caillou sur une case. Elle saute, un pied, puis l'autre. La craie reste jaune, pas grise. Je n'ai pas écrasé. Oui. Les cases tiennent. Chouchou tape des mains, tout petit. Un bateau glisse encore, plus loin. Encore une fois ? Encore. On attend un peu. Sarah revient près du banc. Chouchou reprend le caillou gris. Moi d'abord. Toi d'abord. Chouchou saute. Sarah compte les cases, sans bouger. Merci, Sarah. Le bout est jaune.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1661,7 +1656,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1737,13 +1732,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Victorina a suivi la règle.
-narrateur|Papa l'a rappelée une fois.
-narrateur|Elle a attendu, puis elle a sauté.
-papa|Tu as suivi la règle, Victorina ?
-enfant-f|Oui. Une règle. On attend.
-papa|Bravo. On la rappelle, et on la suit.
-narrateur|La craie blanche reste sur les cases.</t>
+          <t>narrateur|Chouchou arrive au bout des cases.
+copine|C'est bon.
+copine|À toi.
+papa|Sarah, tu peux y aller.
+enfant-f|J'y vais.
+narrateur|Elle pose le caillou sur une case.
+narrateur|Elle saute, un pied, puis l'autre.
+narrateur|La craie reste jaune, pas grise.
+enfant-f|Je n'ai pas écrasé.
+papa|Oui.
+papa|Les cases tiennent.
+narrateur|Chouchou tape des mains, tout petit.
+narrateur|Un bateau glisse encore, plus loin.
+papa|Encore une fois ?
+enfant-f|Encore.
+papa|On attend un peu.
+narrateur|Sarah revient près du banc.
+narrateur|Chouchou reprend le caillou gris.
+copine|Moi d'abord.
+enfant-f|Toi d'abord.
+narrateur|Chouchou saute.
+narrateur|Sarah compte les cases, sans bouger.
+papa|Merci, Sarah.
+enfant-f|Le bout est jaune.</t>
         </is>
       </c>
     </row>
@@ -1770,12 +1782,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On range la craie ? Oui, papa. Papa range la craie dans sa poche. Victorina donne la main. On rentre tout doux ? Oui. Le pigeon est parti. L'ombre du platane reste fraîche. La gourde est encore sur le banc. On la prend ? Oui. Puis on rentre.</t>
+          <t>On s'assoit un peu ? Le banc est chaud. Papa casse une châtaigne. La coque fait un petit bruit. Sarah tient le fruit, tout lisse. Elle est douce. La marelle attend encore. Je rejoue ? Oui. Quand Chouchou a fini. Ils reviennent vers les cases. La rivière brille entre les arbres. Sarah attend, les mains ouvertes. Tu es prête ? Oui, papa. À toi. Sarah saute jusqu'au bout. La dernière case est encore jaune. Chouchou rit, tout bas. On a fini ensemble. Oui. Une après l'autre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>On range la craie ? Oui, papa. Papa range la craie dans sa poche. Victorina donne la main. On rentre tout doux ? Oui. Le pigeon est parti. L'ombre du platane reste fraîche. La gourde est encore sur le banc. On la prend ? Oui. Puis on rentre.</t>
+          <t>On s'assoit un peu ? Le banc est chaud. Papa casse une châtaigne. La coque fait un petit bruit. Sarah tient le fruit, tout lisse. Elle est douce. La marelle attend encore. Je rejoue ? Oui. Quand Chouchou a fini. Ils reviennent vers les cases. La rivière brille entre les arbres. Sarah attend, les mains ouvertes. Tu es prête ? Oui, papa. À toi. Sarah saute jusqu'au bout. La dernière case est encore jaune. Chouchou rit, tout bas. On a fini ensemble. Oui. Une après l'autre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1838,7 +1850,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1910,16 +1922,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>papa|On range la craie ?
+          <t>papa|On s'assoit un peu ?
+enfant-f|Le banc est chaud.
+narrateur|Papa casse une châtaigne.
+narrateur|La coque fait un petit bruit.
+narrateur|Sarah tient le fruit, tout lisse.
+copine|Elle est douce.
+papa|La marelle attend encore.
+enfant-f|Je rejoue ?
+papa|Oui.
+papa|Quand Chouchou a fini.
+narrateur|Ils reviennent vers les cases.
+narrateur|La rivière brille entre les arbres.
+narrateur|Sarah attend, les mains ouvertes.
+papa|Tu es prête ?
 enfant-f|Oui, papa.
-narrateur|Papa range la craie dans sa poche.
-narrateur|Victorina donne la main.
-papa|On rentre tout doux ?
-enfant-f|Oui. Le pigeon est parti.
-narrateur|L'ombre du platane reste fraîche.
-papa|La gourde est encore sur le banc.
-enfant-f|On la prend ?
-papa|Oui. Puis on rentre.</t>
+copine|À toi.
+narrateur|Sarah saute jusqu'au bout.
+narrateur|La dernière case est encore jaune.
+narrateur|Chouchou rit, tout bas.
+enfant-f|On a fini ensemble.
+papa|Oui.
+papa|Une après l'autre.</t>
         </is>
       </c>
     </row>
@@ -1946,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La main de Victorina est un peu blanche. J'ai attendu. Puis j'ai sauté. Oui. Tu as suivi la règle. Bravo, Victorina.</t>
+          <t>Le bout est jaune au soleil. Et toi, tu as attendu. Bravo, Sarah. La rivière brille encore, tout bas. Le caillou gris tient dans la main de Chouchou.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La main de Victorina est un peu blanche. J'ai attendu. Puis j'ai sauté. Oui. Tu as suivi la règle. Bravo, Victorina.</t>
+          <t>Le bout est jaune au soleil. Et toi, tu as attendu. Bravo, Sarah. La rivière brille encore, tout bas. Le caillou gris tient dans la main de Chouchou.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2014,7 +2038,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2086,10 +2110,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|La main de Victorina est un peu blanche.
-enfant-f|J'ai attendu. Puis j'ai sauté.
-papa|Oui. Tu as suivi la règle.
-papa|Bravo, Victorina.</t>
+          <t>enfant-f|Le bout est jaune au soleil.
+papa|Et toi, tu as attendu.
+papa|Bravo, Sarah.
+narrateur|La rivière brille encore, tout bas.
+narrateur|Le caillou gris tient dans la main de Chouchou.</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2160,6 +2185,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
